--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Desktop/kell-tv-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88C310FF-02A3-4620-96EB-F35BAABBA85F}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E145CC93-8E3E-4F7D-A274-C8DE5032A7A4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>TABLERO KPI – MAQUILA KELLOGG'S  |  DATOS DE LA SEMANA</t>
   </si>
@@ -219,16 +219,13 @@
     <t>adelanto septiembre</t>
   </si>
   <si>
+    <t>falta stock</t>
+  </si>
+  <si>
     <t>En ejecucion</t>
   </si>
   <si>
-    <t>falta de totes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adelanto   </t>
-  </si>
-  <si>
-    <t>07/09 al 13/09/2026</t>
+    <t>14/09/2026 al 20/09/2026</t>
   </si>
 </sst>
 </file>
@@ -238,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +325,13 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF1B8A4C"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFF39C12"/>
       <name val="Calibri"/>
@@ -356,6 +360,13 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -447,11 +458,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -489,16 +501,16 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -514,33 +526,41 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{24EDABCD-3CA4-4D3B-9AF0-E231F6619425}"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -840,25 +860,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -876,7 +896,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -886,7 +906,7 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -905,18 +925,19 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="6">
-        <v>86016</v>
+        <f>37400+4610</f>
+        <v>42010</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>12</v>
@@ -927,18 +948,18 @@
         <v>13</v>
       </c>
       <c r="B9" s="6">
-        <v>22632</v>
+        <v>20400</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -952,11 +973,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -970,11 +991,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -988,13 +1009,13 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-    </row>
-    <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+    </row>
+    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1005,54 +1026,57 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-    </row>
-    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+    </row>
+    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="6">
-        <v>3408000</v>
+        <v>2928268</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="6">
-        <v>3600000</v>
+        <v>2659102</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="18"/>
+      <c r="F20" s="25"/>
+    </row>
+    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="8">
-        <v>0.94699999999999995</v>
+        <v>0.91</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="25" t="s">
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-    </row>
-    <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+    </row>
+    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
@@ -1063,14 +1087,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="25" t="s">
+    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-    </row>
-    <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+    </row>
+    <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>38</v>
       </c>
@@ -1081,24 +1105,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
+    <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="30"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1117,20 +1141,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1164,7 +1188,7 @@
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1179,7 +1203,7 @@
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1194,7 +1218,7 @@
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1209,7 +1233,7 @@
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1224,7 +1248,7 @@
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1238,9 +1262,7 @@
         <v>163940</v>
       </c>
       <c r="D9" s="12"/>
-      <c r="E9" s="22" t="s">
-        <v>63</v>
-      </c>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -1254,7 +1276,7 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H10" s="18"/>
     </row>
@@ -1281,11 +1303,11 @@
         <v>205178</v>
       </c>
       <c r="C12" s="11">
-        <v>119240</v>
+        <v>185536</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1302,7 +1324,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="C14" s="14"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
     </row>
@@ -1317,10 +1339,10 @@
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="29"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Desktop/kell-tv-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E145CC93-8E3E-4F7D-A274-C8DE5032A7A4}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EED4817-9791-4B8B-B7F0-A9DCB057598F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>TABLERO KPI – MAQUILA KELLOGG'S  |  DATOS DE LA SEMANA</t>
   </si>
@@ -210,22 +210,16 @@
     <t>Dic</t>
   </si>
   <si>
-    <t>Vamos Mejorando</t>
-  </si>
-  <si>
     <t>Observacion</t>
   </si>
   <si>
-    <t>adelanto septiembre</t>
-  </si>
-  <si>
-    <t>falta stock</t>
-  </si>
-  <si>
     <t>En ejecucion</t>
   </si>
   <si>
     <t>14/09/2026 al 20/09/2026</t>
+  </si>
+  <si>
+    <t>Excelente Equipo</t>
   </si>
 </sst>
 </file>
@@ -536,25 +530,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -869,16 +863,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -896,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -906,7 +900,7 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="26">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -925,11 +919,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -948,18 +942,18 @@
         <v>13</v>
       </c>
       <c r="B9" s="6">
-        <v>20400</v>
+        <v>38000</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -973,11 +967,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -991,11 +985,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -1009,11 +1003,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1027,11 +1021,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
     </row>
     <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1070,11 +1064,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
     </row>
     <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -1088,27 +1082,27 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1141,20 +1135,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1173,7 +1167,7 @@
         <v>45</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1187,9 +1181,7 @@
         <v>275408</v>
       </c>
       <c r="D4" s="12"/>
-      <c r="E4" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
@@ -1202,9 +1194,7 @@
         <v>494770</v>
       </c>
       <c r="D5" s="12"/>
-      <c r="E5" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
@@ -1217,9 +1207,7 @@
         <v>377992</v>
       </c>
       <c r="D6" s="12"/>
-      <c r="E6" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
@@ -1232,9 +1220,7 @@
         <v>277686</v>
       </c>
       <c r="D7" s="12"/>
-      <c r="E7" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
@@ -1247,9 +1233,7 @@
         <v>386288</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
@@ -1275,9 +1259,7 @@
         <v>116278</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="E10" s="22"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1291,9 +1273,7 @@
         <v>429540</v>
       </c>
       <c r="D11" s="13"/>
-      <c r="E11" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="E11" s="22"/>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
@@ -1307,7 +1287,7 @@
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1338,11 +1318,11 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="29"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Desktop/kell-tv-main/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E145CC93-8E3E-4F7D-A274-C8DE5032A7A4}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6D485C2-4FF1-415D-AE79-B50A40B3EDC7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
@@ -536,6 +536,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -546,14 +549,11 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,16 +869,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -906,7 +906,7 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="26">
         <v>46266</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -948,7 +948,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="6">
-        <v>20400</v>
+        <v>38001</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
@@ -1106,23 +1106,23 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1141,20 +1141,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1338,11 +1338,11 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="29"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6D485C2-4FF1-415D-AE79-B50A40B3EDC7}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5492636A-E22D-4073-A4F4-05B8140EA168}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -539,22 +539,22 @@
     <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -869,14 +869,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="31"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
     </row>
@@ -925,11 +925,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -948,18 +948,18 @@
         <v>13</v>
       </c>
       <c r="B9" s="6">
-        <v>38001</v>
+        <v>38002</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -973,11 +973,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -991,11 +991,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -1009,11 +1009,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1027,11 +1027,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
     </row>
     <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1070,11 +1070,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
     </row>
     <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -1088,11 +1088,11 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
@@ -1106,23 +1106,23 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="33"/>
+      <c r="A27" s="27"/>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1141,7 +1141,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="28"/>
@@ -1150,7 +1150,7 @@
       <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="31"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
@@ -1338,7 +1338,7 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5492636A-E22D-4073-A4F4-05B8140EA168}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2602FDEA-5147-414D-9057-3F6DE7C10C98}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,7 +225,7 @@
     <t>En ejecucion</t>
   </si>
   <si>
-    <t>14/09/2026 al 20/09/2026</t>
+    <t>21/09/2026 al 27/09/2026</t>
   </si>
 </sst>
 </file>
@@ -539,7 +539,7 @@
     <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -547,10 +547,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -869,14 +869,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
     </row>
@@ -1106,23 +1106,23 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1141,7 +1141,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="28"/>
@@ -1150,7 +1150,7 @@
       <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2602FDEA-5147-414D-9057-3F6DE7C10C98}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D563A64D-015D-493C-8531-B84DF75A290E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
     <sheet name="PRODUCCION_MENSUAL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -210,9 +210,6 @@
     <t>Dic</t>
   </si>
   <si>
-    <t>Vamos Mejorando</t>
-  </si>
-  <si>
     <t>Observacion</t>
   </si>
   <si>
@@ -226,6 +223,9 @@
   </si>
   <si>
     <t>21/09/2026 al 27/09/2026</t>
+  </si>
+  <si>
+    <t>Excelente Semana</t>
   </si>
 </sst>
 </file>
@@ -539,7 +539,7 @@
     <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -547,10 +547,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -869,14 +869,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32"/>
+      <c r="A2" s="31"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
     </row>
@@ -896,7 +896,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -918,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="5">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>9</v>
@@ -936,8 +936,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="6">
-        <f>37400+4610</f>
-        <v>42010</v>
+        <v>10944</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>12</v>
@@ -948,7 +947,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="6">
-        <v>38002</v>
+        <v>10944</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
@@ -966,7 +965,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="7">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>17</v>
@@ -984,7 +983,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="7">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>20</v>
@@ -1002,7 +1001,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>23</v>
@@ -1020,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>26</v>
@@ -1099,30 +1098,30 @@
         <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="31"/>
+      <c r="A27" s="27"/>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1141,7 +1140,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="28"/>
@@ -1150,7 +1149,7 @@
       <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32"/>
+      <c r="A2" s="31"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
@@ -1173,7 +1172,7 @@
         <v>45</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1188,7 +1187,7 @@
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1203,7 +1202,7 @@
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1218,7 +1217,7 @@
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1233,7 +1232,7 @@
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1248,7 +1247,7 @@
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1276,7 +1275,7 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H10" s="18"/>
     </row>
@@ -1292,7 +1291,7 @@
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1307,7 +1306,7 @@
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D563A64D-015D-493C-8531-B84DF75A290E}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F371629E-53AE-4664-9163-CC85CE41CC13}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>TABLERO KPI – MAQUILA KELLOGG'S  |  DATOS DE LA SEMANA</t>
   </si>
@@ -211,15 +211,6 @@
   </si>
   <si>
     <t>Observacion</t>
-  </si>
-  <si>
-    <t>adelanto septiembre</t>
-  </si>
-  <si>
-    <t>falta stock</t>
-  </si>
-  <si>
-    <t>En ejecucion</t>
   </si>
   <si>
     <t>21/09/2026 al 27/09/2026</t>
@@ -896,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -1098,7 +1089,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>39</v>
@@ -1186,9 +1177,7 @@
         <v>275408</v>
       </c>
       <c r="D4" s="12"/>
-      <c r="E4" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
@@ -1201,9 +1190,7 @@
         <v>494770</v>
       </c>
       <c r="D5" s="12"/>
-      <c r="E5" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
@@ -1216,9 +1203,7 @@
         <v>377992</v>
       </c>
       <c r="D6" s="12"/>
-      <c r="E6" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
@@ -1231,9 +1216,7 @@
         <v>277686</v>
       </c>
       <c r="D7" s="12"/>
-      <c r="E7" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
@@ -1246,9 +1229,7 @@
         <v>386288</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
@@ -1274,9 +1255,7 @@
         <v>116278</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="E10" s="22"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1290,9 +1269,7 @@
         <v>429540</v>
       </c>
       <c r="D11" s="13"/>
-      <c r="E11" s="22" t="s">
-        <v>59</v>
-      </c>
+      <c r="E11" s="22"/>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
@@ -1301,13 +1278,11 @@
       <c r="B12" s="21">
         <v>205178</v>
       </c>
-      <c r="C12" s="11">
-        <v>185536</v>
+      <c r="C12" s="19">
+        <v>205178</v>
       </c>
       <c r="D12" s="15"/>
-      <c r="E12" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="E12" s="22"/>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F371629E-53AE-4664-9163-CC85CE41CC13}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4D9A08A-9E6D-4A1D-B61F-EE95B050772F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>TABLERO KPI – MAQUILA KELLOGG'S  |  DATOS DE LA SEMANA</t>
   </si>
@@ -213,10 +213,13 @@
     <t>Observacion</t>
   </si>
   <si>
-    <t>21/09/2026 al 27/09/2026</t>
-  </si>
-  <si>
     <t>Excelente Semana</t>
+  </si>
+  <si>
+    <t>28/09/2026 al 4/10/2026</t>
+  </si>
+  <si>
+    <t>Octubre</t>
   </si>
 </sst>
 </file>
@@ -530,22 +533,22 @@
     <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -860,14 +863,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="27"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
     </row>
@@ -887,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -897,8 +900,8 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="26">
-        <v>46266</v>
+      <c r="B5" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
@@ -916,18 +919,18 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6">
-        <v>10944</v>
+      <c r="B8" s="3">
+        <v>28320</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>12</v>
@@ -937,19 +940,19 @@
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6">
-        <v>10944</v>
+      <c r="B9" s="3">
+        <v>28320</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -963,11 +966,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -981,11 +984,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -999,11 +1002,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1017,11 +1020,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1060,11 +1063,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
     </row>
     <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -1078,41 +1081,41 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1131,7 +1134,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="29" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="28"/>
@@ -1140,7 +1143,7 @@
       <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
+      <c r="A2" s="27"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
@@ -1288,8 +1291,12 @@
       <c r="A13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="14"/>
+      <c r="B13" s="10">
+        <v>359998</v>
+      </c>
+      <c r="C13" s="19">
+        <v>28320</v>
+      </c>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>
     </row>
@@ -1312,7 +1319,7 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4D9A08A-9E6D-4A1D-B61F-EE95B050772F}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C47C7C-F00F-4CE8-B613-E5B41F3A31B5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="SEMANA" sheetId="1" r:id="rId1"/>
     <sheet name="PRODUCCION_MENSUAL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -216,10 +216,10 @@
     <t>Excelente Semana</t>
   </si>
   <si>
-    <t>28/09/2026 al 4/10/2026</t>
-  </si>
-  <si>
     <t>Octubre</t>
+  </si>
+  <si>
+    <t>5/10/2026 al 11/10/2026</t>
   </si>
 </sst>
 </file>
@@ -457,7 +457,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -533,22 +533,25 @@
     <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -863,14 +866,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
     </row>
@@ -890,7 +893,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -901,7 +904,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
@@ -919,18 +922,18 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="3">
-        <v>28320</v>
+        <v>62960</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>12</v>
@@ -941,18 +944,18 @@
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <v>28320</v>
+        <v>79968</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -966,11 +969,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -984,11 +987,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -1002,11 +1005,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1020,11 +1023,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
     </row>
     <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1063,11 +1066,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
     </row>
     <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -1081,11 +1084,11 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
@@ -1099,7 +1102,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="33"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
     </row>
@@ -1134,7 +1137,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="28"/>
@@ -1143,7 +1146,7 @@
       <c r="E1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
@@ -1284,7 +1287,7 @@
       <c r="C12" s="19">
         <v>205178</v>
       </c>
-      <c r="D12" s="15"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="22"/>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1295,7 +1298,7 @@
         <v>359998</v>
       </c>
       <c r="C13" s="19">
-        <v>28320</v>
+        <v>79968</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>
@@ -1319,7 +1322,7 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C47C7C-F00F-4CE8-B613-E5B41F3A31B5}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{203268FF-3D8B-459B-9EC5-C48547647042}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -533,7 +533,10 @@
     <xf numFmtId="17" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -541,16 +544,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -866,16 +866,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -922,18 +922,18 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="3">
-        <v>62960</v>
+        <v>85440</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>12</v>
@@ -944,18 +944,18 @@
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <v>79968</v>
+        <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -969,11 +969,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -987,11 +987,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -1005,11 +1005,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
@@ -1023,11 +1023,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
     </row>
     <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
@@ -1066,11 +1066,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
@@ -1084,11 +1084,11 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
     </row>
     <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
@@ -1102,23 +1102,23 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="31"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1137,20 +1137,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1287,7 +1287,7 @@
       <c r="C12" s="19">
         <v>205178</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="27"/>
       <c r="E12" s="22"/>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -1298,7 +1298,7 @@
         <v>359998</v>
       </c>
       <c r="C13" s="19">
-        <v>79968</v>
+        <v>91376</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>
@@ -1322,11 +1322,11 @@
       <c r="E15" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{203268FF-3D8B-459B-9EC5-C48547647042}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A89CD9A5-1E33-4FA0-BE67-CA60277ABEE8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,7 +219,7 @@
     <t>Octubre</t>
   </si>
   <si>
-    <t>5/10/2026 al 11/10/2026</t>
+    <t>12/10/2026 al 18/10/2026</t>
   </si>
 </sst>
 </file>
@@ -944,7 +944,8 @@
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <f>1076*16</f>
+        <v>17216</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
@@ -1298,7 +1299,8 @@
         <v>359998</v>
       </c>
       <c r="C13" s="19">
-        <v>91376</v>
+        <f>91376+17216</f>
+        <v>108592</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="16"/>

--- a/data/objetivos.xlsx
+++ b/data/objetivos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc-my.sharepoint.com/personal/controladormultiemp_grupoclc_com/Documents/Documents/GitHub/JESKELL-TV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A89CD9A5-1E33-4FA0-BE67-CA60277ABEE8}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="8_{4DF11E83-7A7F-4557-9B8C-6F15B10F53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55ED57E4-98FF-4ED1-8972-08263C2F8BC5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -536,7 +536,7 @@
     <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -544,10 +544,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -866,14 +866,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32"/>
+      <c r="A2" s="33"/>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
     </row>
@@ -944,8 +944,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <f>1076*16</f>
-        <v>17216</v>
+        <v>51300</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
@@ -1103,23 +1102,23 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="28"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1138,7 +1137,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="29"/>
@@ -1147,7 +1146,7 @@
       <c r="E1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32"/>
+      <c r="A2" s="33"/>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -1296,13 +1295,12 @@
         <v>55</v>
       </c>
       <c r="B13" s="10">
-        <v>359998</v>
-      </c>
-      <c r="C13" s="19">
-        <f>91376+17216</f>
-        <v>108592</v>
-      </c>
-      <c r="D13" s="15"/>
+        <v>202744</v>
+      </c>
+      <c r="C13" s="11">
+        <v>137182</v>
+      </c>
+      <c r="D13" s="27"/>
       <c r="E13" s="16"/>
     </row>
     <row r="14" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
